--- a/docs/zoho-creator/ZIA_UPLOAD.xlsx
+++ b/docs/zoho-creator/ZIA_UPLOAD.xlsx
@@ -469,10 +469,13 @@
           <t xml:space="preserve"># Zia prompt — paste this first
 You are building a Zoho Creator application for Risk Solutions Group (RSG)
 called **RSG Policy Reconciliation**.
-Zia file upload accepts only: .xls .xlsx .xlsm .csv .tsv .ods .mdb .accdb
-.ds .json .numbers (max 2 GB; over 100 MB must be CSV). Do **not** wait for
-Markdown. Upload **one** file: `ZIA_UPLOAD.xlsx` (or `ZIA_UPLOAD.json` /
-`ZIA_UPLOAD.csv`). That file is the full specification.
+Zia can attach PRD, BRD, RFP, and process diagrams. Attach these four PDFs:
+- `PRD_RSG_Policy_Reconciliation.pdf`
+- `BRD_RSG_Policy_Reconciliation.pdf`
+- `RFP_RSG_Policy_Reconciliation.pdf`
+- `PROCESS_DIAGRAMS_RSG_Policy_Reconciliation.pdf`
+Also upload `ZIA_UPLOAD.xlsx` as the field dictionary and Deluge appendix.
+Do not invent fields or verdicts. Build **Phase 1 only**, then stop.
 Read those uploads as the only source of truth (`zia_prompt`,
 `specification_markdown`, `forms`, `picklists`, `deluge`, `sample_records`).
 Build the application **exactly** as specified.

--- a/docs/zoho-creator/ZIA_UPLOAD.xlsx
+++ b/docs/zoho-creator/ZIA_UPLOAD.xlsx
@@ -469,13 +469,9 @@
           <t xml:space="preserve"># Zia prompt — paste this first
 You are building a Zoho Creator application for Risk Solutions Group (RSG)
 called **RSG Policy Reconciliation**.
-Zia can attach PRD, BRD, RFP, and process diagrams. Attach these four PDFs:
-- `PRD_RSG_Policy_Reconciliation.pdf`
-- `BRD_RSG_Policy_Reconciliation.pdf`
-- `RFP_RSG_Policy_Reconciliation.pdf`
-- `PROCESS_DIAGRAMS_RSG_Policy_Reconciliation.pdf`
-Also upload `ZIA_UPLOAD.xlsx` as the field dictionary and Deluge appendix.
-Do not invent fields or verdicts. Build **Phase 1 only**, then stop.
+You are attaching **one document**: `ZIA_UPLOAD.pdf`. It is the complete
+package (PRD + BRD + RFP + process diagrams + field dictionaries + Deluge).
+Build Phase 1 only, then stop.
 Read those uploads as the only source of truth (`zia_prompt`,
 `specification_markdown`, `forms`, `picklists`, `deluge`, `sample_records`).
 Build the application **exactly** as specified.
